--- a/data/trans_dic/DC_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/DC_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 19,31</t>
+          <t>11,08; 19,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,81; 27,49</t>
+          <t>19,84; 27,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,03; 21,79</t>
+          <t>16,16; 21,67</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,7; 24,73</t>
+          <t>15,64; 24,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,62; 42,26</t>
+          <t>34,83; 42,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,98; 32,08</t>
+          <t>25,93; 32,02</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,8; 31,27</t>
+          <t>22,27; 31,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,66; 46,49</t>
+          <t>38,15; 46,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,51; 38,12</t>
+          <t>31,7; 38,11</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,04; 25,01</t>
+          <t>14,77; 24,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,47; 65,7</t>
+          <t>32,02; 65,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,95; 52,99</t>
+          <t>26,61; 51,19</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,32; 24,25</t>
+          <t>15,07; 24,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,9; 39,29</t>
+          <t>15,47; 39,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,05; 30,39</t>
+          <t>18,0; 30,63</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,28; 38,25</t>
+          <t>28,93; 38,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,97; 51,95</t>
+          <t>41,36; 51,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,01; 43,21</t>
+          <t>36,22; 43,08</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,75; 36,69</t>
+          <t>27,66; 35,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>56,26; 82,79</t>
+          <t>56,02; 83,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,01; 70,99</t>
+          <t>43,99; 69,67</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,45; 20,6</t>
+          <t>6,61; 20,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,84; 37,14</t>
+          <t>30,8; 36,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,39; 27,53</t>
+          <t>13,86; 27,71</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,15; 23,88</t>
+          <t>16,48; 23,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39,58; 54,24</t>
+          <t>39,55; 54,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,83; 40,09</t>
+          <t>30,08; 39,43</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34242; 60154</t>
+          <t>34519; 61063</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57379; 79628</t>
+          <t>57456; 80956</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96328; 130959</t>
+          <t>97116; 130274</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81369; 128176</t>
+          <t>81074; 125115</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>178281; 217651</t>
+          <t>179386; 217038</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>268447; 331478</t>
+          <t>267993; 330867</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68890; 98825</t>
+          <t>70396; 100984</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>131490; 162295</t>
+          <t>133194; 163340</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>209623; 253578</t>
+          <t>210843; 253486</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47021; 78174</t>
+          <t>46173; 76287</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149705; 312563</t>
+          <t>152323; 311597</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>204590; 417719</t>
+          <t>209763; 403492</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27384; 43342</t>
+          <t>26930; 43708</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>41158; 101681</t>
+          <t>40041; 101412</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74596; 132965</t>
+          <t>78737; 134016</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>76246; 103128</t>
+          <t>78019; 104133</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>107881; 133548</t>
+          <t>106313; 132833</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>189658; 227592</t>
+          <t>190746; 226905</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>173256; 229065</t>
+          <t>172664; 224633</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>477762; 703066</t>
+          <t>475749; 709549</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>648520; 1046057</t>
+          <t>648194; 1026626</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>59942; 191363</t>
+          <t>61347; 192401</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>221345; 266597</t>
+          <t>221072; 261896</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>236883; 453282</t>
+          <t>228199; 456229</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>593275; 826212</t>
+          <t>570239; 823821</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1469461; 2013722</t>
+          <t>1468343; 2005111</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2139444; 2875621</t>
+          <t>2157419; 2827859</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DC_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/DC_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,08; 19,61</t>
+          <t>11,14; 18,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,84; 27,95</t>
+          <t>19,88; 27,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,16; 21,67</t>
+          <t>16,6; 21,75</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,64; 24,14</t>
+          <t>16,11; 24,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34,83; 42,15</t>
+          <t>34,09; 41,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,93; 32,02</t>
+          <t>26,05; 31,69</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,27; 31,95</t>
+          <t>22,63; 31,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,15; 46,79</t>
+          <t>38,48; 46,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,7; 38,11</t>
+          <t>31,99; 38,26</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 24,41</t>
+          <t>12,99; 22,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,02; 65,5</t>
+          <t>32,71; 41,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,61; 51,19</t>
+          <t>24,38; 30,8</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,07; 24,45</t>
+          <t>14,63; 23,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,47; 39,19</t>
+          <t>32,3; 41,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,0; 30,63</t>
+          <t>24,81; 31,41</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,93; 38,62</t>
+          <t>27,76; 37,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,36; 51,67</t>
+          <t>41,36; 50,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,22; 43,08</t>
+          <t>35,73; 42,73</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,66; 35,98</t>
+          <t>27,82; 35,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>56,02; 83,55</t>
+          <t>54,55; 61,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,99; 69,67</t>
+          <t>42,58; 47,76</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,61; 20,72</t>
+          <t>16,68; 21,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,8; 36,49</t>
+          <t>30,53; 36,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,86; 27,71</t>
+          <t>24,37; 28,19</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,48; 23,81</t>
+          <t>21,51; 24,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39,55; 54,01</t>
+          <t>39,19; 41,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30,08; 39,43</t>
+          <t>30,88; 33,05</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44934</t>
+          <t>46895</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67943</t>
+          <t>73689</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112876</t>
+          <t>120584</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34519; 61063</t>
+          <t>35511; 59739</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57456; 80956</t>
+          <t>62844; 85684</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97116; 130274</t>
+          <t>105417; 138075</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>101805</t>
+          <t>105642</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>196903</t>
+          <t>206498</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>298708</t>
+          <t>312140</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81074; 125115</t>
+          <t>85469; 128961</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>179386; 217038</t>
+          <t>186314; 228305</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>267993; 330867</t>
+          <t>280616; 341300</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83356</t>
+          <t>84418</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>147084</t>
+          <t>152114</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>230440</t>
+          <t>236532</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70396; 100984</t>
+          <t>71505; 100556</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>133194; 163340</t>
+          <t>137148; 167390</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210843; 253486</t>
+          <t>215074; 257273</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>60441</t>
+          <t>64487</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>207689</t>
+          <t>155130</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>268129</t>
+          <t>219617</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46173; 76287</t>
+          <t>48468; 83161</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>152323; 311597</t>
+          <t>138017; 174027</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>209763; 403492</t>
+          <t>193823; 244915</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34499</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79242</t>
+          <t>84295</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113741</t>
+          <t>122501</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26930; 43708</t>
+          <t>30093; 48401</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40041; 101412</t>
+          <t>73946; 95546</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78737; 134016</t>
+          <t>107822; 136482</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>89588</t>
+          <t>87961</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>119239</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208827</t>
+          <t>209715</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>78019; 104133</t>
+          <t>75149; 100673</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>106313; 132833</t>
+          <t>109090; 134155</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>190746; 226905</t>
+          <t>190957; 228384</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>198462</t>
+          <t>229516</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>573965</t>
+          <t>446649</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>772427</t>
+          <t>676165</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>172664; 224633</t>
+          <t>200227; 256038</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>475749; 709549</t>
+          <t>421156; 473428</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>648194; 1026626</t>
+          <t>635144; 712445</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>134512</t>
+          <t>152110</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>241686</t>
+          <t>275232</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>376198</t>
+          <t>427342</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>61347; 192401</t>
+          <t>133090; 174324</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>221072; 261896</t>
+          <t>253807; 299561</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>228199; 456229</t>
+          <t>397098; 459370</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>747597</t>
+          <t>809235</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1633750</t>
+          <t>1515362</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2381347</t>
+          <t>2324597</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>570239; 823821</t>
+          <t>759866; 864592</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1468343; 2005111</t>
+          <t>1464653; 1567010</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2157419; 2827859</t>
+          <t>2244812; 2402482</t>
         </is>
       </c>
     </row>
